--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{D3566A23-DEF6-419B-B116-A4BEFFE36388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9C81922F-5FCE-4D10-B68D-A8049626A2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Product Name</t>
   </si>
@@ -34,12 +34,6 @@
     <t>Price Point (rounded)</t>
   </si>
   <si>
-    <t>Kaveri Necklace Set</t>
-  </si>
-  <si>
-    <t>Raahi Necklace Set</t>
-  </si>
-  <si>
     <t>Supplier Cost</t>
   </si>
   <si>
@@ -62,6 +56,15 @@
   </si>
   <si>
     <t>Profit</t>
+  </si>
+  <si>
+    <t>Kaveri</t>
+  </si>
+  <si>
+    <t>Raahi</t>
+  </si>
+  <si>
+    <t>Saanjh</t>
   </si>
 </sst>
 </file>
@@ -930,10 +933,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692CD7B8-8219-4BAB-B946-0AD4DC2CA2E3}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.44140625" bestFit="1" customWidth="1"/>
@@ -952,31 +955,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>2</v>
@@ -987,7 +990,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>450</v>
@@ -1032,7 +1035,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>1240</v>
@@ -1073,6 +1076,51 @@
       <c r="L3" t="str">
         <f>"₹"&amp;TEXT(G3,"#,##0")</f>
         <v>₹5,999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>1495</v>
+      </c>
+      <c r="C4">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>150</v>
+      </c>
+      <c r="E4">
+        <f>B4+C4+D4</f>
+        <v>1670</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <f>ROUNDUP((E4*F4)/500,0)*500-1</f>
+        <v>6999</v>
+      </c>
+      <c r="H4">
+        <f>G4*2%</f>
+        <v>139.97999999999999</v>
+      </c>
+      <c r="I4">
+        <f>G4-H4</f>
+        <v>6859.02</v>
+      </c>
+      <c r="J4">
+        <f>I4-E4</f>
+        <v>5189.0200000000004</v>
+      </c>
+      <c r="K4" s="1">
+        <f>J4/G4</f>
+        <v>0.74139448492641813</v>
+      </c>
+      <c r="L4" t="str">
+        <f>"₹"&amp;TEXT(G4,"#,##0")</f>
+        <v>₹6,999</v>
       </c>
     </row>
   </sheetData>

--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{9C81922F-5FCE-4D10-B68D-A8049626A2F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B57990BB-C5C4-4537-98EA-6C8073A58DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Product Name</t>
   </si>
@@ -65,6 +65,12 @@
   </si>
   <si>
     <t>Saanjh</t>
+  </si>
+  <si>
+    <t>Adaa</t>
+  </si>
+  <si>
+    <t>Ruhani</t>
   </si>
 </sst>
 </file>
@@ -933,7 +939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692CD7B8-8219-4BAB-B946-0AD4DC2CA2E3}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -1006,31 +1012,31 @@
         <v>625</v>
       </c>
       <c r="F2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2">
         <f>ROUNDUP((E2*F2)/500,0)*500-1</f>
-        <v>2499</v>
+        <v>1999</v>
       </c>
       <c r="H2">
         <f>G2*2%</f>
-        <v>49.980000000000004</v>
+        <v>39.980000000000004</v>
       </c>
       <c r="I2">
         <f>G2-H2</f>
-        <v>2449.02</v>
+        <v>1959.02</v>
       </c>
       <c r="J2">
         <f>I2-E2</f>
-        <v>1824.02</v>
+        <v>1334.02</v>
       </c>
       <c r="K2" s="1">
         <f>J2/G2</f>
-        <v>0.7298999599839936</v>
+        <v>0.66734367183591792</v>
       </c>
       <c r="L2" t="str">
         <f>"₹"&amp;TEXT(G2,"#,##0")</f>
-        <v>₹2,499</v>
+        <v>₹1,999</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -1051,31 +1057,31 @@
         <v>1415</v>
       </c>
       <c r="F3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3">
         <f>ROUNDUP((E3*F3)/500,0)*500-1</f>
-        <v>5999</v>
+        <v>4499</v>
       </c>
       <c r="H3">
         <f>G3*2%</f>
-        <v>119.98</v>
+        <v>89.98</v>
       </c>
       <c r="I3">
         <f>G3-H3</f>
-        <v>5879.02</v>
+        <v>4409.0200000000004</v>
       </c>
       <c r="J3">
         <f>I3-E3</f>
-        <v>4464.0200000000004</v>
+        <v>2994.0200000000004</v>
       </c>
       <c r="K3" s="1">
         <f>J3/G3</f>
-        <v>0.74412735455909329</v>
+        <v>0.66548566348077365</v>
       </c>
       <c r="L3" t="str">
         <f>"₹"&amp;TEXT(G3,"#,##0")</f>
-        <v>₹5,999</v>
+        <v>₹4,499</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -1096,31 +1102,121 @@
         <v>1670</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4">
         <f>ROUNDUP((E4*F4)/500,0)*500-1</f>
-        <v>6999</v>
+        <v>5499</v>
       </c>
       <c r="H4">
         <f>G4*2%</f>
-        <v>139.97999999999999</v>
+        <v>109.98</v>
       </c>
       <c r="I4">
         <f>G4-H4</f>
-        <v>6859.02</v>
+        <v>5389.02</v>
       </c>
       <c r="J4">
         <f>I4-E4</f>
-        <v>5189.0200000000004</v>
+        <v>3719.0200000000004</v>
       </c>
       <c r="K4" s="1">
         <f>J4/G4</f>
-        <v>0.74139448492641813</v>
+        <v>0.67630841971267508</v>
       </c>
       <c r="L4" t="str">
         <f>"₹"&amp;TEXT(G4,"#,##0")</f>
-        <v>₹6,999</v>
+        <v>₹5,499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <v>1134</v>
+      </c>
+      <c r="C5">
+        <v>25</v>
+      </c>
+      <c r="D5">
+        <v>150</v>
+      </c>
+      <c r="E5">
+        <f>B5+C5+D5</f>
+        <v>1309</v>
+      </c>
+      <c r="F5">
+        <v>3</v>
+      </c>
+      <c r="G5">
+        <f>ROUNDUP((E5*F5)/500,0)*500-1</f>
+        <v>3999</v>
+      </c>
+      <c r="H5">
+        <f>G5*2%</f>
+        <v>79.98</v>
+      </c>
+      <c r="I5">
+        <f>G5-H5</f>
+        <v>3919.02</v>
+      </c>
+      <c r="J5">
+        <f>I5-E5</f>
+        <v>2610.02</v>
+      </c>
+      <c r="K5" s="1">
+        <f>J5/G5</f>
+        <v>0.65266816704176045</v>
+      </c>
+      <c r="L5" t="str">
+        <f>"₹"&amp;TEXT(G5,"#,##0")</f>
+        <v>₹3,999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <v>2100</v>
+      </c>
+      <c r="C6">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>150</v>
+      </c>
+      <c r="E6">
+        <f>B6+C6+D6</f>
+        <v>2275</v>
+      </c>
+      <c r="F6">
+        <v>1.75</v>
+      </c>
+      <c r="G6">
+        <f>ROUNDUP((E6*F6)/500,0)*500-1</f>
+        <v>3999</v>
+      </c>
+      <c r="H6">
+        <f>G6*2%</f>
+        <v>79.98</v>
+      </c>
+      <c r="I6">
+        <f>G6-H6</f>
+        <v>3919.02</v>
+      </c>
+      <c r="J6">
+        <f>I6-E6</f>
+        <v>1644.02</v>
+      </c>
+      <c r="K6" s="1">
+        <f>J6/G6</f>
+        <v>0.41110777694423606</v>
+      </c>
+      <c r="L6" t="str">
+        <f>"₹"&amp;TEXT(G6,"#,##0")</f>
+        <v>₹3,999</v>
       </c>
     </row>
   </sheetData>

--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B57990BB-C5C4-4537-98EA-6C8073A58DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0674D6E0-614F-4B80-828B-1369AC9A670F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>

--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0674D6E0-614F-4B80-828B-1369AC9A670F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F06BD3C-0D48-4615-8558-C35C34D321B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>
   <sheets>
     <sheet name="pricing-calculator" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -939,7 +952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692CD7B8-8219-4BAB-B946-0AD4DC2CA2E3}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -956,7 +969,7 @@
     <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -994,7 +1007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1002,14 +1015,14 @@
         <v>450</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>150</v>
       </c>
       <c r="E2">
         <f>B2+C2+D2</f>
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -1028,18 +1041,25 @@
       </c>
       <c r="J2">
         <f>I2-E2</f>
-        <v>1334.02</v>
+        <v>1309.02</v>
       </c>
       <c r="K2" s="1">
         <f>J2/G2</f>
-        <v>0.66734367183591792</v>
+        <v>0.65483741870935464</v>
       </c>
       <c r="L2" t="str">
         <f>"₹"&amp;TEXT(G2,"#,##0")</f>
         <v>₹1,999</v>
       </c>
+      <c r="N2">
+        <v>1999</v>
+      </c>
+      <c r="O2">
+        <f>G2-N2</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1047,14 +1067,14 @@
         <v>1240</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D3">
         <v>150</v>
       </c>
       <c r="E3">
         <f>B3+C3+D3</f>
-        <v>1415</v>
+        <v>1440</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -1073,18 +1093,25 @@
       </c>
       <c r="J3">
         <f>I3-E3</f>
-        <v>2994.0200000000004</v>
+        <v>2969.0200000000004</v>
       </c>
       <c r="K3" s="1">
         <f>J3/G3</f>
-        <v>0.66548566348077365</v>
+        <v>0.65992887308290737</v>
       </c>
       <c r="L3" t="str">
         <f>"₹"&amp;TEXT(G3,"#,##0")</f>
         <v>₹4,499</v>
       </c>
+      <c r="N3">
+        <v>4499</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O6" si="0">G3-N3</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1092,14 +1119,14 @@
         <v>1495</v>
       </c>
       <c r="C4">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D4">
         <v>150</v>
       </c>
       <c r="E4">
         <f>B4+C4+D4</f>
-        <v>1670</v>
+        <v>1695</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -1118,18 +1145,25 @@
       </c>
       <c r="J4">
         <f>I4-E4</f>
-        <v>3719.0200000000004</v>
+        <v>3694.0200000000004</v>
       </c>
       <c r="K4" s="1">
         <f>J4/G4</f>
-        <v>0.67630841971267508</v>
+        <v>0.67176213857064926</v>
       </c>
       <c r="L4" t="str">
         <f>"₹"&amp;TEXT(G4,"#,##0")</f>
         <v>₹5,499</v>
       </c>
+      <c r="N4">
+        <v>5499</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1137,14 +1171,14 @@
         <v>1134</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D5">
         <v>150</v>
       </c>
       <c r="E5">
         <f>B5+C5+D5</f>
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -1163,18 +1197,25 @@
       </c>
       <c r="J5">
         <f>I5-E5</f>
-        <v>2610.02</v>
+        <v>2605.02</v>
       </c>
       <c r="K5" s="1">
         <f>J5/G5</f>
-        <v>0.65266816704176045</v>
+        <v>0.65141785446361589</v>
       </c>
       <c r="L5" t="str">
         <f>"₹"&amp;TEXT(G5,"#,##0")</f>
         <v>₹3,999</v>
       </c>
+      <c r="N5">
+        <v>3999</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1182,14 +1223,14 @@
         <v>2100</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D6">
         <v>150</v>
       </c>
       <c r="E6">
         <f>B6+C6+D6</f>
-        <v>2275</v>
+        <v>2280</v>
       </c>
       <c r="F6">
         <v>1.75</v>
@@ -1208,15 +1249,22 @@
       </c>
       <c r="J6">
         <f>I6-E6</f>
-        <v>1644.02</v>
+        <v>1639.02</v>
       </c>
       <c r="K6" s="1">
         <f>J6/G6</f>
-        <v>0.41110777694423606</v>
+        <v>0.4098574643660915</v>
       </c>
       <c r="L6" t="str">
         <f>"₹"&amp;TEXT(G6,"#,##0")</f>
         <v>₹3,999</v>
+      </c>
+      <c r="N6">
+        <v>3999</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F06BD3C-0D48-4615-8558-C35C34D321B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F984C922-6B7F-42D1-A934-68AD0248A023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Product Name</t>
   </si>
@@ -84,6 +84,15 @@
   </si>
   <si>
     <t>Ruhani</t>
+  </si>
+  <si>
+    <t>Kanak</t>
+  </si>
+  <si>
+    <t>Virasat</t>
+  </si>
+  <si>
+    <t>Sunehri</t>
   </si>
 </sst>
 </file>
@@ -952,7 +961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692CD7B8-8219-4BAB-B946-0AD4DC2CA2E3}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -969,7 +978,7 @@
     <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1007,7 +1016,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -1051,15 +1060,8 @@
         <f>"₹"&amp;TEXT(G2,"#,##0")</f>
         <v>₹1,999</v>
       </c>
-      <c r="N2">
-        <v>1999</v>
-      </c>
-      <c r="O2">
-        <f>G2-N2</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>13</v>
       </c>
@@ -1103,15 +1105,8 @@
         <f>"₹"&amp;TEXT(G3,"#,##0")</f>
         <v>₹4,499</v>
       </c>
-      <c r="N3">
-        <v>4499</v>
-      </c>
-      <c r="O3">
-        <f t="shared" ref="O3:O6" si="0">G3-N3</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1155,15 +1150,8 @@
         <f>"₹"&amp;TEXT(G4,"#,##0")</f>
         <v>₹5,499</v>
       </c>
-      <c r="N4">
-        <v>5499</v>
-      </c>
-      <c r="O4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -1207,15 +1195,8 @@
         <f>"₹"&amp;TEXT(G5,"#,##0")</f>
         <v>₹3,999</v>
       </c>
-      <c r="N5">
-        <v>3999</v>
-      </c>
-      <c r="O5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -1259,12 +1240,140 @@
         <f>"₹"&amp;TEXT(G6,"#,##0")</f>
         <v>₹3,999</v>
       </c>
-      <c r="N6">
-        <v>3999</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="0"/>
-        <v>0</v>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <v>472</v>
+      </c>
+      <c r="C7">
+        <v>30</v>
+      </c>
+      <c r="D7">
+        <v>150</v>
+      </c>
+      <c r="E7">
+        <f>B7+C7+D7</f>
+        <v>652</v>
+      </c>
+      <c r="F7">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <f>ROUNDUP((E7*F7)/500,0)*500-1</f>
+        <v>1999</v>
+      </c>
+      <c r="H7">
+        <f>G7*2%</f>
+        <v>39.980000000000004</v>
+      </c>
+      <c r="I7">
+        <f>G7-H7</f>
+        <v>1959.02</v>
+      </c>
+      <c r="J7">
+        <f>I7-E7</f>
+        <v>1307.02</v>
+      </c>
+      <c r="K7" s="1">
+        <f>J7/G7</f>
+        <v>0.65383691845922964</v>
+      </c>
+      <c r="L7" t="str">
+        <f>"₹"&amp;TEXT(G7,"#,##0")</f>
+        <v>₹1,999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>71</v>
+      </c>
+      <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>150</v>
+      </c>
+      <c r="E8">
+        <f>B8+C8+D8</f>
+        <v>251</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <f>ROUNDUP((E8*F8)/500,0)*500-1</f>
+        <v>999</v>
+      </c>
+      <c r="H8">
+        <f>G8*2%</f>
+        <v>19.98</v>
+      </c>
+      <c r="I8">
+        <f>G8-H8</f>
+        <v>979.02</v>
+      </c>
+      <c r="J8">
+        <f>I8-E8</f>
+        <v>728.02</v>
+      </c>
+      <c r="K8" s="1">
+        <f>J8/G8</f>
+        <v>0.72874874874874873</v>
+      </c>
+      <c r="L8" t="str">
+        <f>"₹"&amp;TEXT(G8,"#,##0")</f>
+        <v>₹999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9">
+        <v>110</v>
+      </c>
+      <c r="C9">
+        <v>30</v>
+      </c>
+      <c r="D9">
+        <v>150</v>
+      </c>
+      <c r="E9">
+        <f>B9+C9+D9</f>
+        <v>290</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <f>ROUNDUP((E9*F9)/500,0)*500-1</f>
+        <v>999</v>
+      </c>
+      <c r="H9">
+        <f>G9*2%</f>
+        <v>19.98</v>
+      </c>
+      <c r="I9">
+        <f>G9-H9</f>
+        <v>979.02</v>
+      </c>
+      <c r="J9">
+        <f>I9-E9</f>
+        <v>689.02</v>
+      </c>
+      <c r="K9" s="1">
+        <f>J9/G9</f>
+        <v>0.68970970970970968</v>
+      </c>
+      <c r="L9" t="str">
+        <f>"₹"&amp;TEXT(G9,"#,##0")</f>
+        <v>₹999</v>
       </c>
     </row>
   </sheetData>

--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F984C922-6B7F-42D1-A934-68AD0248A023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B228A280-2A9A-46CA-8656-8AD6E6C2C687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>
@@ -1249,41 +1249,41 @@
         <v>472</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>150</v>
       </c>
       <c r="E7">
         <f>B7+C7+D7</f>
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
         <f>ROUNDUP((E7*F7)/500,0)*500-1</f>
-        <v>1999</v>
+        <v>2499</v>
       </c>
       <c r="H7">
         <f>G7*2%</f>
-        <v>39.980000000000004</v>
+        <v>49.980000000000004</v>
       </c>
       <c r="I7">
         <f>G7-H7</f>
-        <v>1959.02</v>
+        <v>2449.02</v>
       </c>
       <c r="J7">
         <f>I7-E7</f>
-        <v>1307.02</v>
+        <v>1777.02</v>
       </c>
       <c r="K7" s="1">
         <f>J7/G7</f>
-        <v>0.65383691845922964</v>
+        <v>0.71109243697478985</v>
       </c>
       <c r="L7" t="str">
         <f>"₹"&amp;TEXT(G7,"#,##0")</f>
-        <v>₹1,999</v>
+        <v>₹2,499</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -1294,14 +1294,14 @@
         <v>71</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>150</v>
       </c>
       <c r="E8">
         <f>B8+C8+D8</f>
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="F8">
         <v>3</v>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="J8">
         <f>I8-E8</f>
-        <v>728.02</v>
+        <v>708.02</v>
       </c>
       <c r="K8" s="1">
         <f>J8/G8</f>
-        <v>0.72874874874874873</v>
+        <v>0.70872872872872872</v>
       </c>
       <c r="L8" t="str">
         <f>"₹"&amp;TEXT(G8,"#,##0")</f>
@@ -1339,14 +1339,14 @@
         <v>110</v>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D9">
         <v>150</v>
       </c>
       <c r="E9">
         <f>B9+C9+D9</f>
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -1365,11 +1365,11 @@
       </c>
       <c r="J9">
         <f>I9-E9</f>
-        <v>689.02</v>
+        <v>669.02</v>
       </c>
       <c r="K9" s="1">
         <f>J9/G9</f>
-        <v>0.68970970970970968</v>
+        <v>0.66968968968968967</v>
       </c>
       <c r="L9" t="str">
         <f>"₹"&amp;TEXT(G9,"#,##0")</f>

--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B228A280-2A9A-46CA-8656-8AD6E6C2C687}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EAE58C-4359-41DE-BE8B-0A99C179132A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Product Name</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Sunehri</t>
+  </si>
+  <si>
+    <t>Antara</t>
   </si>
 </sst>
 </file>
@@ -961,7 +964,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692CD7B8-8219-4BAB-B946-0AD4DC2CA2E3}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -1376,6 +1379,51 @@
         <v>₹999</v>
       </c>
     </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10">
+        <v>1070</v>
+      </c>
+      <c r="C10">
+        <v>50</v>
+      </c>
+      <c r="D10">
+        <v>150</v>
+      </c>
+      <c r="E10">
+        <f>B10+C10+D10</f>
+        <v>1270</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <f>ROUNDUP((E10*F10)/500,0)*500-1</f>
+        <v>3999</v>
+      </c>
+      <c r="H10">
+        <f>G10*2%</f>
+        <v>79.98</v>
+      </c>
+      <c r="I10">
+        <f>G10-H10</f>
+        <v>3919.02</v>
+      </c>
+      <c r="J10">
+        <f>I10-E10</f>
+        <v>2649.02</v>
+      </c>
+      <c r="K10" s="1">
+        <f>J10/G10</f>
+        <v>0.66242060515128787</v>
+      </c>
+      <c r="L10" t="str">
+        <f>"₹"&amp;TEXT(G10,"#,##0")</f>
+        <v>₹3,999</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45EAE58C-4359-41DE-BE8B-0A99C179132A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA86490-8BAA-44EA-9026-4E0D57BF8F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Product Name</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>Antara</t>
+  </si>
+  <si>
+    <t>Chandni</t>
+  </si>
+  <si>
+    <t>Rajsi</t>
   </si>
 </sst>
 </file>
@@ -964,7 +970,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692CD7B8-8219-4BAB-B946-0AD4DC2CA2E3}">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -1021,10 +1027,10 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>450</v>
+        <v>71</v>
       </c>
       <c r="C2">
         <v>50</v>
@@ -1034,42 +1040,42 @@
       </c>
       <c r="E2">
         <f>B2+C2+D2</f>
-        <v>650</v>
+        <v>271</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
         <f>ROUNDUP((E2*F2)/500,0)*500-1</f>
-        <v>1999</v>
+        <v>999</v>
       </c>
       <c r="H2">
         <f>G2*2%</f>
-        <v>39.980000000000004</v>
+        <v>19.98</v>
       </c>
       <c r="I2">
         <f>G2-H2</f>
-        <v>1959.02</v>
+        <v>979.02</v>
       </c>
       <c r="J2">
         <f>I2-E2</f>
-        <v>1309.02</v>
+        <v>708.02</v>
       </c>
       <c r="K2" s="1">
         <f>J2/G2</f>
-        <v>0.65483741870935464</v>
+        <v>0.70872872872872872</v>
       </c>
       <c r="L2" t="str">
         <f>"₹"&amp;TEXT(G2,"#,##0")</f>
-        <v>₹1,999</v>
+        <v>₹999</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>1240</v>
+        <v>110</v>
       </c>
       <c r="C3">
         <v>50</v>
@@ -1079,42 +1085,42 @@
       </c>
       <c r="E3">
         <f>B3+C3+D3</f>
-        <v>1440</v>
+        <v>310</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
         <f>ROUNDUP((E3*F3)/500,0)*500-1</f>
-        <v>4499</v>
+        <v>999</v>
       </c>
       <c r="H3">
         <f>G3*2%</f>
-        <v>89.98</v>
+        <v>19.98</v>
       </c>
       <c r="I3">
         <f>G3-H3</f>
-        <v>4409.0200000000004</v>
+        <v>979.02</v>
       </c>
       <c r="J3">
         <f>I3-E3</f>
-        <v>2969.0200000000004</v>
+        <v>669.02</v>
       </c>
       <c r="K3" s="1">
         <f>J3/G3</f>
-        <v>0.65992887308290737</v>
+        <v>0.66968968968968967</v>
       </c>
       <c r="L3" t="str">
         <f>"₹"&amp;TEXT(G3,"#,##0")</f>
-        <v>₹4,499</v>
+        <v>₹999</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4">
-        <v>1495</v>
+        <v>450</v>
       </c>
       <c r="C4">
         <v>50</v>
@@ -1124,222 +1130,222 @@
       </c>
       <c r="E4">
         <f>B4+C4+D4</f>
-        <v>1695</v>
+        <v>650</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4">
         <f>ROUNDUP((E4*F4)/500,0)*500-1</f>
-        <v>5499</v>
+        <v>1999</v>
       </c>
       <c r="H4">
         <f>G4*2%</f>
-        <v>109.98</v>
+        <v>39.980000000000004</v>
       </c>
       <c r="I4">
         <f>G4-H4</f>
-        <v>5389.02</v>
+        <v>1959.02</v>
       </c>
       <c r="J4">
         <f>I4-E4</f>
-        <v>3694.0200000000004</v>
+        <v>1309.02</v>
       </c>
       <c r="K4" s="1">
         <f>J4/G4</f>
-        <v>0.67176213857064926</v>
+        <v>0.65483741870935464</v>
       </c>
       <c r="L4" t="str">
         <f>"₹"&amp;TEXT(G4,"#,##0")</f>
-        <v>₹5,499</v>
+        <v>₹1,999</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5">
-        <v>1134</v>
+        <v>472</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D5">
         <v>150</v>
       </c>
       <c r="E5">
         <f>B5+C5+D5</f>
-        <v>1314</v>
+        <v>672</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
       <c r="G5">
         <f>ROUNDUP((E5*F5)/500,0)*500-1</f>
-        <v>3999</v>
+        <v>2499</v>
       </c>
       <c r="H5">
         <f>G5*2%</f>
-        <v>79.98</v>
+        <v>49.980000000000004</v>
       </c>
       <c r="I5">
         <f>G5-H5</f>
-        <v>3919.02</v>
+        <v>2449.02</v>
       </c>
       <c r="J5">
         <f>I5-E5</f>
-        <v>2605.02</v>
+        <v>1777.02</v>
       </c>
       <c r="K5" s="1">
         <f>J5/G5</f>
-        <v>0.65141785446361589</v>
+        <v>0.71109243697478985</v>
       </c>
       <c r="L5" t="str">
         <f>"₹"&amp;TEXT(G5,"#,##0")</f>
-        <v>₹3,999</v>
+        <v>₹2,499</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B6">
-        <v>2100</v>
+        <v>654</v>
       </c>
       <c r="C6">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D6">
         <v>150</v>
       </c>
       <c r="E6">
         <f>B6+C6+D6</f>
-        <v>2280</v>
+        <v>854</v>
       </c>
       <c r="F6">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="G6">
         <f>ROUNDUP((E6*F6)/500,0)*500-1</f>
-        <v>3999</v>
+        <v>2999</v>
       </c>
       <c r="H6">
         <f>G6*2%</f>
-        <v>79.98</v>
+        <v>59.980000000000004</v>
       </c>
       <c r="I6">
         <f>G6-H6</f>
-        <v>3919.02</v>
+        <v>2939.02</v>
       </c>
       <c r="J6">
         <f>I6-E6</f>
-        <v>1639.02</v>
+        <v>2085.02</v>
       </c>
       <c r="K6" s="1">
         <f>J6/G6</f>
-        <v>0.4098574643660915</v>
+        <v>0.69523841280426812</v>
       </c>
       <c r="L6" t="str">
         <f>"₹"&amp;TEXT(G6,"#,##0")</f>
-        <v>₹3,999</v>
+        <v>₹2,999</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>472</v>
+        <v>1134</v>
       </c>
       <c r="C7">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D7">
         <v>150</v>
       </c>
       <c r="E7">
         <f>B7+C7+D7</f>
-        <v>672</v>
+        <v>1314</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
         <f>ROUNDUP((E7*F7)/500,0)*500-1</f>
-        <v>2499</v>
+        <v>3999</v>
       </c>
       <c r="H7">
         <f>G7*2%</f>
-        <v>49.980000000000004</v>
+        <v>79.98</v>
       </c>
       <c r="I7">
         <f>G7-H7</f>
-        <v>2449.02</v>
+        <v>3919.02</v>
       </c>
       <c r="J7">
         <f>I7-E7</f>
-        <v>1777.02</v>
+        <v>2605.02</v>
       </c>
       <c r="K7" s="1">
         <f>J7/G7</f>
-        <v>0.71109243697478985</v>
+        <v>0.65141785446361589</v>
       </c>
       <c r="L7" t="str">
         <f>"₹"&amp;TEXT(G7,"#,##0")</f>
-        <v>₹2,499</v>
+        <v>₹3,999</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>71</v>
+        <v>2100</v>
       </c>
       <c r="C8">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>150</v>
       </c>
       <c r="E8">
         <f>B8+C8+D8</f>
-        <v>271</v>
+        <v>2280</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>1.75</v>
       </c>
       <c r="G8">
         <f>ROUNDUP((E8*F8)/500,0)*500-1</f>
-        <v>999</v>
+        <v>3999</v>
       </c>
       <c r="H8">
         <f>G8*2%</f>
-        <v>19.98</v>
+        <v>79.98</v>
       </c>
       <c r="I8">
         <f>G8-H8</f>
-        <v>979.02</v>
+        <v>3919.02</v>
       </c>
       <c r="J8">
         <f>I8-E8</f>
-        <v>708.02</v>
+        <v>1639.02</v>
       </c>
       <c r="K8" s="1">
         <f>J8/G8</f>
-        <v>0.70872872872872872</v>
+        <v>0.4098574643660915</v>
       </c>
       <c r="L8" t="str">
         <f>"₹"&amp;TEXT(G8,"#,##0")</f>
-        <v>₹999</v>
+        <v>₹3,999</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>110</v>
+        <v>1070</v>
       </c>
       <c r="C9">
         <v>50</v>
@@ -1349,42 +1355,42 @@
       </c>
       <c r="E9">
         <f>B9+C9+D9</f>
-        <v>310</v>
+        <v>1270</v>
       </c>
       <c r="F9">
         <v>3</v>
       </c>
       <c r="G9">
         <f>ROUNDUP((E9*F9)/500,0)*500-1</f>
-        <v>999</v>
+        <v>3999</v>
       </c>
       <c r="H9">
         <f>G9*2%</f>
-        <v>19.98</v>
+        <v>79.98</v>
       </c>
       <c r="I9">
         <f>G9-H9</f>
-        <v>979.02</v>
+        <v>3919.02</v>
       </c>
       <c r="J9">
         <f>I9-E9</f>
-        <v>669.02</v>
+        <v>2649.02</v>
       </c>
       <c r="K9" s="1">
         <f>J9/G9</f>
-        <v>0.66968968968968967</v>
+        <v>0.66242060515128787</v>
       </c>
       <c r="L9" t="str">
         <f>"₹"&amp;TEXT(G9,"#,##0")</f>
-        <v>₹999</v>
+        <v>₹3,999</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -1394,7 +1400,7 @@
       </c>
       <c r="E10">
         <f>B10+C10+D10</f>
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="F10">
         <v>3</v>
@@ -1413,18 +1419,111 @@
       </c>
       <c r="J10">
         <f>I10-E10</f>
-        <v>2649.02</v>
+        <v>2650.02</v>
       </c>
       <c r="K10" s="1">
         <f>J10/G10</f>
-        <v>0.66242060515128787</v>
+        <v>0.66267066766691674</v>
       </c>
       <c r="L10" t="str">
         <f>"₹"&amp;TEXT(G10,"#,##0")</f>
         <v>₹3,999</v>
       </c>
     </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11">
+        <v>1240</v>
+      </c>
+      <c r="C11">
+        <v>50</v>
+      </c>
+      <c r="D11">
+        <v>150</v>
+      </c>
+      <c r="E11">
+        <f>B11+C11+D11</f>
+        <v>1440</v>
+      </c>
+      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="G11">
+        <f>ROUNDUP((E11*F11)/500,0)*500-1</f>
+        <v>4499</v>
+      </c>
+      <c r="H11">
+        <f>G11*2%</f>
+        <v>89.98</v>
+      </c>
+      <c r="I11">
+        <f>G11-H11</f>
+        <v>4409.0200000000004</v>
+      </c>
+      <c r="J11">
+        <f>I11-E11</f>
+        <v>2969.0200000000004</v>
+      </c>
+      <c r="K11" s="1">
+        <f>J11/G11</f>
+        <v>0.65992887308290737</v>
+      </c>
+      <c r="L11" t="str">
+        <f>"₹"&amp;TEXT(G11,"#,##0")</f>
+        <v>₹4,499</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12">
+        <v>1495</v>
+      </c>
+      <c r="C12">
+        <v>50</v>
+      </c>
+      <c r="D12">
+        <v>150</v>
+      </c>
+      <c r="E12">
+        <f>B12+C12+D12</f>
+        <v>1695</v>
+      </c>
+      <c r="F12">
+        <v>3</v>
+      </c>
+      <c r="G12">
+        <f>ROUNDUP((E12*F12)/500,0)*500-1</f>
+        <v>5499</v>
+      </c>
+      <c r="H12">
+        <f>G12*2%</f>
+        <v>109.98</v>
+      </c>
+      <c r="I12">
+        <f>G12-H12</f>
+        <v>5389.02</v>
+      </c>
+      <c r="J12">
+        <f>I12-E12</f>
+        <v>3694.0200000000004</v>
+      </c>
+      <c r="K12" s="1">
+        <f>J12/G12</f>
+        <v>0.67176213857064926</v>
+      </c>
+      <c r="L12" t="str">
+        <f>"₹"&amp;TEXT(G12,"#,##0")</f>
+        <v>₹5,499</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L12">
+    <sortCondition ref="G2:G12"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA86490-8BAA-44EA-9026-4E0D57BF8F28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FDF650-D643-446F-90A2-A35C92903CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Product Name</t>
   </si>
@@ -102,6 +102,21 @@
   </si>
   <si>
     <t>Rajsi</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>Blossom</t>
+  </si>
+  <si>
+    <t>Grace</t>
+  </si>
+  <si>
+    <t>Ziya</t>
+  </si>
+  <si>
+    <t>Iris</t>
   </si>
 </sst>
 </file>
@@ -970,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692CD7B8-8219-4BAB-B946-0AD4DC2CA2E3}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -1117,10 +1132,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="B4">
-        <v>450</v>
+        <v>145</v>
       </c>
       <c r="C4">
         <v>50</v>
@@ -1130,42 +1145,42 @@
       </c>
       <c r="E4">
         <f>B4+C4+D4</f>
-        <v>650</v>
+        <v>345</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4">
         <f>ROUNDUP((E4*F4)/500,0)*500-1</f>
-        <v>1999</v>
+        <v>1499</v>
       </c>
       <c r="H4">
         <f>G4*2%</f>
-        <v>39.980000000000004</v>
+        <v>29.98</v>
       </c>
       <c r="I4">
         <f>G4-H4</f>
-        <v>1959.02</v>
+        <v>1469.02</v>
       </c>
       <c r="J4">
         <f>I4-E4</f>
-        <v>1309.02</v>
+        <v>1124.02</v>
       </c>
       <c r="K4" s="1">
         <f>J4/G4</f>
-        <v>0.65483741870935464</v>
+        <v>0.74984656437625086</v>
       </c>
       <c r="L4" t="str">
         <f>"₹"&amp;TEXT(G4,"#,##0")</f>
-        <v>₹1,999</v>
+        <v>₹1,499</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B5">
-        <v>472</v>
+        <v>425</v>
       </c>
       <c r="C5">
         <v>50</v>
@@ -1175,42 +1190,42 @@
       </c>
       <c r="E5">
         <f>B5+C5+D5</f>
-        <v>672</v>
+        <v>625</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5">
         <f>ROUNDUP((E5*F5)/500,0)*500-1</f>
-        <v>2499</v>
+        <v>1499</v>
       </c>
       <c r="H5">
         <f>G5*2%</f>
-        <v>49.980000000000004</v>
+        <v>29.98</v>
       </c>
       <c r="I5">
         <f>G5-H5</f>
-        <v>2449.02</v>
+        <v>1469.02</v>
       </c>
       <c r="J5">
         <f>I5-E5</f>
-        <v>1777.02</v>
+        <v>844.02</v>
       </c>
       <c r="K5" s="1">
         <f>J5/G5</f>
-        <v>0.71109243697478985</v>
+        <v>0.56305537024683117</v>
       </c>
       <c r="L5" t="str">
         <f>"₹"&amp;TEXT(G5,"#,##0")</f>
-        <v>₹2,499</v>
+        <v>₹1,499</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B6">
-        <v>654</v>
+        <v>380</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -1220,132 +1235,132 @@
       </c>
       <c r="E6">
         <f>B6+C6+D6</f>
-        <v>854</v>
+        <v>580</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G6">
         <f>ROUNDUP((E6*F6)/500,0)*500-1</f>
-        <v>2999</v>
+        <v>1499</v>
       </c>
       <c r="H6">
         <f>G6*2%</f>
-        <v>59.980000000000004</v>
+        <v>29.98</v>
       </c>
       <c r="I6">
         <f>G6-H6</f>
-        <v>2939.02</v>
+        <v>1469.02</v>
       </c>
       <c r="J6">
         <f>I6-E6</f>
-        <v>2085.02</v>
+        <v>889.02</v>
       </c>
       <c r="K6" s="1">
         <f>J6/G6</f>
-        <v>0.69523841280426812</v>
+        <v>0.59307538358905931</v>
       </c>
       <c r="L6" t="str">
         <f>"₹"&amp;TEXT(G6,"#,##0")</f>
-        <v>₹2,999</v>
+        <v>₹1,499</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B7">
-        <v>1134</v>
+        <v>450</v>
       </c>
       <c r="C7">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D7">
         <v>150</v>
       </c>
       <c r="E7">
         <f>B7+C7+D7</f>
-        <v>1314</v>
+        <v>650</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
         <f>ROUNDUP((E7*F7)/500,0)*500-1</f>
-        <v>3999</v>
+        <v>1999</v>
       </c>
       <c r="H7">
         <f>G7*2%</f>
-        <v>79.98</v>
+        <v>39.980000000000004</v>
       </c>
       <c r="I7">
         <f>G7-H7</f>
-        <v>3919.02</v>
+        <v>1959.02</v>
       </c>
       <c r="J7">
         <f>I7-E7</f>
-        <v>2605.02</v>
+        <v>1309.02</v>
       </c>
       <c r="K7" s="1">
         <f>J7/G7</f>
-        <v>0.65141785446361589</v>
+        <v>0.65483741870935464</v>
       </c>
       <c r="L7" t="str">
         <f>"₹"&amp;TEXT(G7,"#,##0")</f>
-        <v>₹3,999</v>
+        <v>₹1,999</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B8">
-        <v>2100</v>
+        <v>456</v>
       </c>
       <c r="C8">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D8">
         <v>150</v>
       </c>
       <c r="E8">
         <f>B8+C8+D8</f>
-        <v>2280</v>
+        <v>656</v>
       </c>
       <c r="F8">
-        <v>1.75</v>
+        <v>3</v>
       </c>
       <c r="G8">
         <f>ROUNDUP((E8*F8)/500,0)*500-1</f>
-        <v>3999</v>
+        <v>1999</v>
       </c>
       <c r="H8">
         <f>G8*2%</f>
-        <v>79.98</v>
+        <v>39.980000000000004</v>
       </c>
       <c r="I8">
         <f>G8-H8</f>
-        <v>3919.02</v>
+        <v>1959.02</v>
       </c>
       <c r="J8">
         <f>I8-E8</f>
-        <v>1639.02</v>
+        <v>1303.02</v>
       </c>
       <c r="K8" s="1">
         <f>J8/G8</f>
-        <v>0.4098574643660915</v>
+        <v>0.65183591795897944</v>
       </c>
       <c r="L8" t="str">
         <f>"₹"&amp;TEXT(G8,"#,##0")</f>
-        <v>₹3,999</v>
+        <v>₹1,999</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B9">
-        <v>1070</v>
+        <v>480</v>
       </c>
       <c r="C9">
         <v>50</v>
@@ -1355,42 +1370,42 @@
       </c>
       <c r="E9">
         <f>B9+C9+D9</f>
-        <v>1270</v>
+        <v>680</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G9">
         <f>ROUNDUP((E9*F9)/500,0)*500-1</f>
-        <v>3999</v>
+        <v>1999</v>
       </c>
       <c r="H9">
         <f>G9*2%</f>
-        <v>79.98</v>
+        <v>39.980000000000004</v>
       </c>
       <c r="I9">
         <f>G9-H9</f>
-        <v>3919.02</v>
+        <v>1959.02</v>
       </c>
       <c r="J9">
         <f>I9-E9</f>
-        <v>2649.02</v>
+        <v>1279.02</v>
       </c>
       <c r="K9" s="1">
         <f>J9/G9</f>
-        <v>0.66242060515128787</v>
+        <v>0.63982991495747876</v>
       </c>
       <c r="L9" t="str">
         <f>"₹"&amp;TEXT(G9,"#,##0")</f>
-        <v>₹3,999</v>
+        <v>₹1,999</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B10">
-        <v>1069</v>
+        <v>472</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -1400,42 +1415,42 @@
       </c>
       <c r="E10">
         <f>B10+C10+D10</f>
-        <v>1269</v>
+        <v>672</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10">
         <f>ROUNDUP((E10*F10)/500,0)*500-1</f>
-        <v>3999</v>
+        <v>2499</v>
       </c>
       <c r="H10">
         <f>G10*2%</f>
-        <v>79.98</v>
+        <v>49.980000000000004</v>
       </c>
       <c r="I10">
         <f>G10-H10</f>
-        <v>3919.02</v>
+        <v>2449.02</v>
       </c>
       <c r="J10">
         <f>I10-E10</f>
-        <v>2650.02</v>
+        <v>1777.02</v>
       </c>
       <c r="K10" s="1">
         <f>J10/G10</f>
-        <v>0.66267066766691674</v>
+        <v>0.71109243697478985</v>
       </c>
       <c r="L10" t="str">
         <f>"₹"&amp;TEXT(G10,"#,##0")</f>
-        <v>₹3,999</v>
+        <v>₹2,499</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>1240</v>
+        <v>654</v>
       </c>
       <c r="C11">
         <v>50</v>
@@ -1445,84 +1460,309 @@
       </c>
       <c r="E11">
         <f>B11+C11+D11</f>
-        <v>1440</v>
+        <v>854</v>
       </c>
       <c r="F11">
         <v>3</v>
       </c>
       <c r="G11">
         <f>ROUNDUP((E11*F11)/500,0)*500-1</f>
-        <v>4499</v>
+        <v>2999</v>
       </c>
       <c r="H11">
         <f>G11*2%</f>
-        <v>89.98</v>
+        <v>59.980000000000004</v>
       </c>
       <c r="I11">
         <f>G11-H11</f>
-        <v>4409.0200000000004</v>
+        <v>2939.02</v>
       </c>
       <c r="J11">
         <f>I11-E11</f>
-        <v>2969.0200000000004</v>
+        <v>2085.02</v>
       </c>
       <c r="K11" s="1">
         <f>J11/G11</f>
-        <v>0.65992887308290737</v>
+        <v>0.69523841280426812</v>
       </c>
       <c r="L11" t="str">
         <f>"₹"&amp;TEXT(G11,"#,##0")</f>
-        <v>₹4,499</v>
+        <v>₹2,999</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B12">
-        <v>1495</v>
+        <v>1134</v>
       </c>
       <c r="C12">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D12">
         <v>150</v>
       </c>
       <c r="E12">
         <f>B12+C12+D12</f>
-        <v>1695</v>
+        <v>1314</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12">
         <f>ROUNDUP((E12*F12)/500,0)*500-1</f>
-        <v>5499</v>
+        <v>3999</v>
       </c>
       <c r="H12">
         <f>G12*2%</f>
-        <v>109.98</v>
+        <v>79.98</v>
       </c>
       <c r="I12">
         <f>G12-H12</f>
-        <v>5389.02</v>
+        <v>3919.02</v>
       </c>
       <c r="J12">
         <f>I12-E12</f>
-        <v>3694.0200000000004</v>
+        <v>2605.02</v>
       </c>
       <c r="K12" s="1">
         <f>J12/G12</f>
-        <v>0.67176213857064926</v>
+        <v>0.65141785446361589</v>
       </c>
       <c r="L12" t="str">
         <f>"₹"&amp;TEXT(G12,"#,##0")</f>
+        <v>₹3,999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13">
+        <v>2100</v>
+      </c>
+      <c r="C13">
+        <v>30</v>
+      </c>
+      <c r="D13">
+        <v>150</v>
+      </c>
+      <c r="E13">
+        <f>B13+C13+D13</f>
+        <v>2280</v>
+      </c>
+      <c r="F13">
+        <v>1.75</v>
+      </c>
+      <c r="G13">
+        <f>ROUNDUP((E13*F13)/500,0)*500-1</f>
+        <v>3999</v>
+      </c>
+      <c r="H13">
+        <f>G13*2%</f>
+        <v>79.98</v>
+      </c>
+      <c r="I13">
+        <f>G13-H13</f>
+        <v>3919.02</v>
+      </c>
+      <c r="J13">
+        <f>I13-E13</f>
+        <v>1639.02</v>
+      </c>
+      <c r="K13" s="1">
+        <f>J13/G13</f>
+        <v>0.4098574643660915</v>
+      </c>
+      <c r="L13" t="str">
+        <f>"₹"&amp;TEXT(G13,"#,##0")</f>
+        <v>₹3,999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <v>1070</v>
+      </c>
+      <c r="C14">
+        <v>50</v>
+      </c>
+      <c r="D14">
+        <v>150</v>
+      </c>
+      <c r="E14">
+        <f>B14+C14+D14</f>
+        <v>1270</v>
+      </c>
+      <c r="F14">
+        <v>3</v>
+      </c>
+      <c r="G14">
+        <f>ROUNDUP((E14*F14)/500,0)*500-1</f>
+        <v>3999</v>
+      </c>
+      <c r="H14">
+        <f>G14*2%</f>
+        <v>79.98</v>
+      </c>
+      <c r="I14">
+        <f>G14-H14</f>
+        <v>3919.02</v>
+      </c>
+      <c r="J14">
+        <f>I14-E14</f>
+        <v>2649.02</v>
+      </c>
+      <c r="K14" s="1">
+        <f>J14/G14</f>
+        <v>0.66242060515128787</v>
+      </c>
+      <c r="L14" t="str">
+        <f>"₹"&amp;TEXT(G14,"#,##0")</f>
+        <v>₹3,999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15">
+        <v>1069</v>
+      </c>
+      <c r="C15">
+        <v>50</v>
+      </c>
+      <c r="D15">
+        <v>150</v>
+      </c>
+      <c r="E15">
+        <f>B15+C15+D15</f>
+        <v>1269</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15">
+        <f>ROUNDUP((E15*F15)/500,0)*500-1</f>
+        <v>3999</v>
+      </c>
+      <c r="H15">
+        <f>G15*2%</f>
+        <v>79.98</v>
+      </c>
+      <c r="I15">
+        <f>G15-H15</f>
+        <v>3919.02</v>
+      </c>
+      <c r="J15">
+        <f>I15-E15</f>
+        <v>2650.02</v>
+      </c>
+      <c r="K15" s="1">
+        <f>J15/G15</f>
+        <v>0.66267066766691674</v>
+      </c>
+      <c r="L15" t="str">
+        <f>"₹"&amp;TEXT(G15,"#,##0")</f>
+        <v>₹3,999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16">
+        <v>1240</v>
+      </c>
+      <c r="C16">
+        <v>50</v>
+      </c>
+      <c r="D16">
+        <v>150</v>
+      </c>
+      <c r="E16">
+        <f>B16+C16+D16</f>
+        <v>1440</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16">
+        <f>ROUNDUP((E16*F16)/500,0)*500-1</f>
+        <v>4499</v>
+      </c>
+      <c r="H16">
+        <f>G16*2%</f>
+        <v>89.98</v>
+      </c>
+      <c r="I16">
+        <f>G16-H16</f>
+        <v>4409.0200000000004</v>
+      </c>
+      <c r="J16">
+        <f>I16-E16</f>
+        <v>2969.0200000000004</v>
+      </c>
+      <c r="K16" s="1">
+        <f>J16/G16</f>
+        <v>0.65992887308290737</v>
+      </c>
+      <c r="L16" t="str">
+        <f>"₹"&amp;TEXT(G16,"#,##0")</f>
+        <v>₹4,499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17">
+        <v>1495</v>
+      </c>
+      <c r="C17">
+        <v>50</v>
+      </c>
+      <c r="D17">
+        <v>150</v>
+      </c>
+      <c r="E17">
+        <f>B17+C17+D17</f>
+        <v>1695</v>
+      </c>
+      <c r="F17">
+        <v>3</v>
+      </c>
+      <c r="G17">
+        <f>ROUNDUP((E17*F17)/500,0)*500-1</f>
+        <v>5499</v>
+      </c>
+      <c r="H17">
+        <f>G17*2%</f>
+        <v>109.98</v>
+      </c>
+      <c r="I17">
+        <f>G17-H17</f>
+        <v>5389.02</v>
+      </c>
+      <c r="J17">
+        <f>I17-E17</f>
+        <v>3694.0200000000004</v>
+      </c>
+      <c r="K17" s="1">
+        <f>J17/G17</f>
+        <v>0.67176213857064926</v>
+      </c>
+      <c r="L17" t="str">
+        <f>"₹"&amp;TEXT(G17,"#,##0")</f>
         <v>₹5,499</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L12">
-    <sortCondition ref="G2:G12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L17">
+    <sortCondition ref="G2:G17"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/business/pricing-calculator.xlsx
+++ b/business/pricing-calculator.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahujadiv\Desktop\Team\Automations\JBG\jewels-by-geetika\business\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74FDF650-D643-446F-90A2-A35C92903CBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D80954C4-EE78-4AAE-8105-20C8F406F975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3EA1E2F3-88D9-406C-AEBC-3B66D1D0E7C6}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Product Name</t>
   </si>
@@ -68,9 +68,6 @@
     <t>Net Revenue</t>
   </si>
   <si>
-    <t>Profit</t>
-  </si>
-  <si>
     <t>Kaveri</t>
   </si>
   <si>
@@ -117,6 +114,12 @@
   </si>
   <si>
     <t>Iris</t>
+  </si>
+  <si>
+    <t>Golden Lobster</t>
+  </si>
+  <si>
+    <t>Ideal Profit</t>
   </si>
 </sst>
 </file>
@@ -985,7 +988,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{692CD7B8-8219-4BAB-B946-0AD4DC2CA2E3}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
@@ -997,9 +1000,8 @@
     <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -1031,7 +1033,7 @@
         <v>10</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>2</v>
@@ -1042,7 +1044,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2">
         <v>71</v>
@@ -1054,40 +1056,40 @@
         <v>150</v>
       </c>
       <c r="E2">
-        <f>B2+C2+D2</f>
+        <f t="shared" ref="E2:E17" si="0">B2+C2+D2</f>
         <v>271</v>
       </c>
       <c r="F2">
         <v>3</v>
       </c>
       <c r="G2">
-        <f>ROUNDUP((E2*F2)/500,0)*500-1</f>
+        <f t="shared" ref="G2:G17" si="1">ROUNDUP((E2*F2)/500,0)*500-1</f>
         <v>999</v>
       </c>
       <c r="H2">
-        <f>G2*2%</f>
+        <f t="shared" ref="H2:H18" si="2">G2*2%</f>
         <v>19.98</v>
       </c>
       <c r="I2">
-        <f>G2-H2</f>
+        <f t="shared" ref="I2:I17" si="3">G2-H2</f>
         <v>979.02</v>
       </c>
       <c r="J2">
-        <f>I2-E2</f>
+        <f t="shared" ref="J2:J17" si="4">I2-E2</f>
         <v>708.02</v>
       </c>
       <c r="K2" s="1">
-        <f>J2/G2</f>
+        <f t="shared" ref="K2:K17" si="5">J2/G2</f>
         <v>0.70872872872872872</v>
       </c>
       <c r="L2" t="str">
-        <f>"₹"&amp;TEXT(G2,"#,##0")</f>
+        <f t="shared" ref="L2:L17" si="6">"₹"&amp;TEXT(G2,"#,##0")</f>
         <v>₹999</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3">
         <v>110</v>
@@ -1099,40 +1101,40 @@
         <v>150</v>
       </c>
       <c r="E3">
-        <f>B3+C3+D3</f>
+        <f t="shared" si="0"/>
         <v>310</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
       <c r="G3">
-        <f>ROUNDUP((E3*F3)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>999</v>
       </c>
       <c r="H3">
-        <f>G3*2%</f>
+        <f t="shared" si="2"/>
         <v>19.98</v>
       </c>
       <c r="I3">
-        <f>G3-H3</f>
+        <f t="shared" si="3"/>
         <v>979.02</v>
       </c>
       <c r="J3">
-        <f>I3-E3</f>
+        <f t="shared" si="4"/>
         <v>669.02</v>
       </c>
       <c r="K3" s="1">
-        <f>J3/G3</f>
+        <f t="shared" si="5"/>
         <v>0.66968968968968967</v>
       </c>
       <c r="L3" t="str">
-        <f>"₹"&amp;TEXT(G3,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹999</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>145</v>
@@ -1144,40 +1146,40 @@
         <v>150</v>
       </c>
       <c r="E4">
-        <f>B4+C4+D4</f>
+        <f t="shared" si="0"/>
         <v>345</v>
       </c>
       <c r="F4">
         <v>3</v>
       </c>
       <c r="G4">
-        <f>ROUNDUP((E4*F4)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>1499</v>
       </c>
       <c r="H4">
-        <f>G4*2%</f>
+        <f t="shared" si="2"/>
         <v>29.98</v>
       </c>
       <c r="I4">
-        <f>G4-H4</f>
+        <f t="shared" si="3"/>
         <v>1469.02</v>
       </c>
       <c r="J4">
-        <f>I4-E4</f>
+        <f t="shared" si="4"/>
         <v>1124.02</v>
       </c>
       <c r="K4" s="1">
-        <f>J4/G4</f>
+        <f t="shared" si="5"/>
         <v>0.74984656437625086</v>
       </c>
       <c r="L4" t="str">
-        <f>"₹"&amp;TEXT(G4,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹1,499</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5">
         <v>425</v>
@@ -1189,40 +1191,40 @@
         <v>150</v>
       </c>
       <c r="E5">
-        <f>B5+C5+D5</f>
+        <f t="shared" si="0"/>
         <v>625</v>
       </c>
       <c r="F5">
         <v>2</v>
       </c>
       <c r="G5">
-        <f>ROUNDUP((E5*F5)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>1499</v>
       </c>
       <c r="H5">
-        <f>G5*2%</f>
+        <f t="shared" si="2"/>
         <v>29.98</v>
       </c>
       <c r="I5">
-        <f>G5-H5</f>
+        <f t="shared" si="3"/>
         <v>1469.02</v>
       </c>
       <c r="J5">
-        <f>I5-E5</f>
+        <f t="shared" si="4"/>
         <v>844.02</v>
       </c>
       <c r="K5" s="1">
-        <f>J5/G5</f>
+        <f t="shared" si="5"/>
         <v>0.56305537024683117</v>
       </c>
       <c r="L5" t="str">
-        <f>"₹"&amp;TEXT(G5,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹1,499</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B6">
         <v>380</v>
@@ -1234,40 +1236,40 @@
         <v>150</v>
       </c>
       <c r="E6">
-        <f>B6+C6+D6</f>
+        <f t="shared" si="0"/>
         <v>580</v>
       </c>
       <c r="F6">
         <v>2.5</v>
       </c>
       <c r="G6">
-        <f>ROUNDUP((E6*F6)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>1499</v>
       </c>
       <c r="H6">
-        <f>G6*2%</f>
+        <f t="shared" si="2"/>
         <v>29.98</v>
       </c>
       <c r="I6">
-        <f>G6-H6</f>
+        <f t="shared" si="3"/>
         <v>1469.02</v>
       </c>
       <c r="J6">
-        <f>I6-E6</f>
+        <f t="shared" si="4"/>
         <v>889.02</v>
       </c>
       <c r="K6" s="1">
-        <f>J6/G6</f>
+        <f t="shared" si="5"/>
         <v>0.59307538358905931</v>
       </c>
       <c r="L6" t="str">
-        <f>"₹"&amp;TEXT(G6,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹1,499</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7">
         <v>450</v>
@@ -1279,40 +1281,40 @@
         <v>150</v>
       </c>
       <c r="E7">
-        <f>B7+C7+D7</f>
+        <f t="shared" si="0"/>
         <v>650</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7">
-        <f>ROUNDUP((E7*F7)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>1999</v>
       </c>
       <c r="H7">
-        <f>G7*2%</f>
+        <f t="shared" si="2"/>
         <v>39.980000000000004</v>
       </c>
       <c r="I7">
-        <f>G7-H7</f>
+        <f t="shared" si="3"/>
         <v>1959.02</v>
       </c>
       <c r="J7">
-        <f>I7-E7</f>
+        <f t="shared" si="4"/>
         <v>1309.02</v>
       </c>
       <c r="K7" s="1">
-        <f>J7/G7</f>
+        <f t="shared" si="5"/>
         <v>0.65483741870935464</v>
       </c>
       <c r="L7" t="str">
-        <f>"₹"&amp;TEXT(G7,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹1,999</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8">
         <v>456</v>
@@ -1324,40 +1326,40 @@
         <v>150</v>
       </c>
       <c r="E8">
-        <f>B8+C8+D8</f>
+        <f t="shared" si="0"/>
         <v>656</v>
       </c>
       <c r="F8">
         <v>3</v>
       </c>
       <c r="G8">
-        <f>ROUNDUP((E8*F8)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>1999</v>
       </c>
       <c r="H8">
-        <f>G8*2%</f>
+        <f t="shared" si="2"/>
         <v>39.980000000000004</v>
       </c>
       <c r="I8">
-        <f>G8-H8</f>
+        <f t="shared" si="3"/>
         <v>1959.02</v>
       </c>
       <c r="J8">
-        <f>I8-E8</f>
+        <f t="shared" si="4"/>
         <v>1303.02</v>
       </c>
       <c r="K8" s="1">
-        <f>J8/G8</f>
+        <f t="shared" si="5"/>
         <v>0.65183591795897944</v>
       </c>
       <c r="L8" t="str">
-        <f>"₹"&amp;TEXT(G8,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹1,999</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B9">
         <v>480</v>
@@ -1369,40 +1371,40 @@
         <v>150</v>
       </c>
       <c r="E9">
-        <f>B9+C9+D9</f>
+        <f t="shared" si="0"/>
         <v>680</v>
       </c>
       <c r="F9">
         <v>2.5</v>
       </c>
       <c r="G9">
-        <f>ROUNDUP((E9*F9)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>1999</v>
       </c>
       <c r="H9">
-        <f>G9*2%</f>
+        <f t="shared" si="2"/>
         <v>39.980000000000004</v>
       </c>
       <c r="I9">
-        <f>G9-H9</f>
+        <f t="shared" si="3"/>
         <v>1959.02</v>
       </c>
       <c r="J9">
-        <f>I9-E9</f>
+        <f t="shared" si="4"/>
         <v>1279.02</v>
       </c>
       <c r="K9" s="1">
-        <f>J9/G9</f>
+        <f t="shared" si="5"/>
         <v>0.63982991495747876</v>
       </c>
       <c r="L9" t="str">
-        <f>"₹"&amp;TEXT(G9,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹1,999</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>472</v>
@@ -1414,40 +1416,40 @@
         <v>150</v>
       </c>
       <c r="E10">
-        <f>B10+C10+D10</f>
+        <f t="shared" si="0"/>
         <v>672</v>
       </c>
       <c r="F10">
         <v>3</v>
       </c>
       <c r="G10">
-        <f>ROUNDUP((E10*F10)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>2499</v>
       </c>
       <c r="H10">
-        <f>G10*2%</f>
+        <f t="shared" si="2"/>
         <v>49.980000000000004</v>
       </c>
       <c r="I10">
-        <f>G10-H10</f>
+        <f t="shared" si="3"/>
         <v>2449.02</v>
       </c>
       <c r="J10">
-        <f>I10-E10</f>
+        <f t="shared" si="4"/>
         <v>1777.02</v>
       </c>
       <c r="K10" s="1">
-        <f>J10/G10</f>
+        <f t="shared" si="5"/>
         <v>0.71109243697478985</v>
       </c>
       <c r="L10" t="str">
-        <f>"₹"&amp;TEXT(G10,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹2,499</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>654</v>
@@ -1459,40 +1461,40 @@
         <v>150</v>
       </c>
       <c r="E11">
-        <f>B11+C11+D11</f>
+        <f t="shared" si="0"/>
         <v>854</v>
       </c>
       <c r="F11">
         <v>3</v>
       </c>
       <c r="G11">
-        <f>ROUNDUP((E11*F11)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>2999</v>
       </c>
       <c r="H11">
-        <f>G11*2%</f>
+        <f t="shared" si="2"/>
         <v>59.980000000000004</v>
       </c>
       <c r="I11">
-        <f>G11-H11</f>
+        <f t="shared" si="3"/>
         <v>2939.02</v>
       </c>
       <c r="J11">
-        <f>I11-E11</f>
+        <f t="shared" si="4"/>
         <v>2085.02</v>
       </c>
       <c r="K11" s="1">
-        <f>J11/G11</f>
+        <f t="shared" si="5"/>
         <v>0.69523841280426812</v>
       </c>
       <c r="L11" t="str">
-        <f>"₹"&amp;TEXT(G11,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹2,999</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12">
         <v>1134</v>
@@ -1504,40 +1506,40 @@
         <v>150</v>
       </c>
       <c r="E12">
-        <f>B12+C12+D12</f>
+        <f t="shared" si="0"/>
         <v>1314</v>
       </c>
       <c r="F12">
         <v>3</v>
       </c>
       <c r="G12">
-        <f>ROUNDUP((E12*F12)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>3999</v>
       </c>
       <c r="H12">
-        <f>G12*2%</f>
+        <f t="shared" si="2"/>
         <v>79.98</v>
       </c>
       <c r="I12">
-        <f>G12-H12</f>
+        <f t="shared" si="3"/>
         <v>3919.02</v>
       </c>
       <c r="J12">
-        <f>I12-E12</f>
+        <f t="shared" si="4"/>
         <v>2605.02</v>
       </c>
       <c r="K12" s="1">
-        <f>J12/G12</f>
+        <f t="shared" si="5"/>
         <v>0.65141785446361589</v>
       </c>
       <c r="L12" t="str">
-        <f>"₹"&amp;TEXT(G12,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹3,999</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B13">
         <v>2100</v>
@@ -1549,40 +1551,40 @@
         <v>150</v>
       </c>
       <c r="E13">
-        <f>B13+C13+D13</f>
+        <f t="shared" si="0"/>
         <v>2280</v>
       </c>
       <c r="F13">
         <v>1.75</v>
       </c>
       <c r="G13">
-        <f>ROUNDUP((E13*F13)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>3999</v>
       </c>
       <c r="H13">
-        <f>G13*2%</f>
+        <f t="shared" si="2"/>
         <v>79.98</v>
       </c>
       <c r="I13">
-        <f>G13-H13</f>
+        <f t="shared" si="3"/>
         <v>3919.02</v>
       </c>
       <c r="J13">
-        <f>I13-E13</f>
+        <f t="shared" si="4"/>
         <v>1639.02</v>
       </c>
       <c r="K13" s="1">
-        <f>J13/G13</f>
+        <f t="shared" si="5"/>
         <v>0.4098574643660915</v>
       </c>
       <c r="L13" t="str">
-        <f>"₹"&amp;TEXT(G13,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹3,999</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14">
         <v>1070</v>
@@ -1594,40 +1596,40 @@
         <v>150</v>
       </c>
       <c r="E14">
-        <f>B14+C14+D14</f>
+        <f t="shared" si="0"/>
         <v>1270</v>
       </c>
       <c r="F14">
         <v>3</v>
       </c>
       <c r="G14">
-        <f>ROUNDUP((E14*F14)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>3999</v>
       </c>
       <c r="H14">
-        <f>G14*2%</f>
+        <f t="shared" si="2"/>
         <v>79.98</v>
       </c>
       <c r="I14">
-        <f>G14-H14</f>
+        <f t="shared" si="3"/>
         <v>3919.02</v>
       </c>
       <c r="J14">
-        <f>I14-E14</f>
+        <f t="shared" si="4"/>
         <v>2649.02</v>
       </c>
       <c r="K14" s="1">
-        <f>J14/G14</f>
+        <f t="shared" si="5"/>
         <v>0.66242060515128787</v>
       </c>
       <c r="L14" t="str">
-        <f>"₹"&amp;TEXT(G14,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹3,999</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15">
         <v>1069</v>
@@ -1639,40 +1641,40 @@
         <v>150</v>
       </c>
       <c r="E15">
-        <f>B15+C15+D15</f>
+        <f t="shared" si="0"/>
         <v>1269</v>
       </c>
       <c r="F15">
         <v>3</v>
       </c>
       <c r="G15">
-        <f>ROUNDUP((E15*F15)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>3999</v>
       </c>
       <c r="H15">
-        <f>G15*2%</f>
+        <f t="shared" si="2"/>
         <v>79.98</v>
       </c>
       <c r="I15">
-        <f>G15-H15</f>
+        <f t="shared" si="3"/>
         <v>3919.02</v>
       </c>
       <c r="J15">
-        <f>I15-E15</f>
+        <f t="shared" si="4"/>
         <v>2650.02</v>
       </c>
       <c r="K15" s="1">
-        <f>J15/G15</f>
+        <f t="shared" si="5"/>
         <v>0.66267066766691674</v>
       </c>
       <c r="L15" t="str">
-        <f>"₹"&amp;TEXT(G15,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹3,999</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16">
         <v>1240</v>
@@ -1684,40 +1686,40 @@
         <v>150</v>
       </c>
       <c r="E16">
-        <f>B16+C16+D16</f>
+        <f t="shared" si="0"/>
         <v>1440</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
       <c r="G16">
-        <f>ROUNDUP((E16*F16)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>4499</v>
       </c>
       <c r="H16">
-        <f>G16*2%</f>
+        <f t="shared" si="2"/>
         <v>89.98</v>
       </c>
       <c r="I16">
-        <f>G16-H16</f>
+        <f t="shared" si="3"/>
         <v>4409.0200000000004</v>
       </c>
       <c r="J16">
-        <f>I16-E16</f>
+        <f t="shared" si="4"/>
         <v>2969.0200000000004</v>
       </c>
       <c r="K16" s="1">
-        <f>J16/G16</f>
+        <f t="shared" si="5"/>
         <v>0.65992887308290737</v>
       </c>
       <c r="L16" t="str">
-        <f>"₹"&amp;TEXT(G16,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹4,499</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17">
         <v>1495</v>
@@ -1729,35 +1731,80 @@
         <v>150</v>
       </c>
       <c r="E17">
-        <f>B17+C17+D17</f>
+        <f t="shared" si="0"/>
         <v>1695</v>
       </c>
       <c r="F17">
         <v>3</v>
       </c>
       <c r="G17">
-        <f>ROUNDUP((E17*F17)/500,0)*500-1</f>
+        <f t="shared" si="1"/>
         <v>5499</v>
       </c>
       <c r="H17">
-        <f>G17*2%</f>
+        <f t="shared" si="2"/>
         <v>109.98</v>
       </c>
       <c r="I17">
-        <f>G17-H17</f>
+        <f t="shared" si="3"/>
         <v>5389.02</v>
       </c>
       <c r="J17">
-        <f>I17-E17</f>
+        <f t="shared" si="4"/>
         <v>3694.0200000000004</v>
       </c>
       <c r="K17" s="1">
-        <f>J17/G17</f>
+        <f t="shared" si="5"/>
         <v>0.67176213857064926</v>
       </c>
       <c r="L17" t="str">
-        <f>"₹"&amp;TEXT(G17,"#,##0")</f>
+        <f t="shared" si="6"/>
         <v>₹5,499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>768</v>
+      </c>
+      <c r="C18">
+        <v>50</v>
+      </c>
+      <c r="D18">
+        <v>150</v>
+      </c>
+      <c r="E18">
+        <f t="shared" ref="E18" si="7">B18+C18+D18</f>
+        <v>968</v>
+      </c>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <f t="shared" ref="G18" si="8">ROUNDUP((E18*F18)/500,0)*500-1</f>
+        <v>2999</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="2"/>
+        <v>59.980000000000004</v>
+      </c>
+      <c r="I18">
+        <f t="shared" ref="I18" si="9">G18-H18</f>
+        <v>2939.02</v>
+      </c>
+      <c r="J18">
+        <f t="shared" ref="J18" si="10">I18-E18</f>
+        <v>1971.02</v>
+      </c>
+      <c r="K18" s="1">
+        <f t="shared" ref="K18" si="11">J18/G18</f>
+        <v>0.65722574191397132</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" ref="L18" si="12">"₹"&amp;TEXT(G18,"#,##0")</f>
+        <v>₹2,999</v>
       </c>
     </row>
   </sheetData>
